--- a/data/CMPA_template_sk.xlsx
+++ b/data/CMPA_template_sk.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\horkyt\Desktop\CMPA vzory\Completion rate předěláno na Kvalita zásahu\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\horkyt\Desktop\repos\news-web2\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{014B9495-868D-434B-9837-4D7D251FB637}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{573C05E6-6182-48B3-A02A-F342A90505C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19005" yWindow="960" windowWidth="17475" windowHeight="17985" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6375" yWindow="4395" windowWidth="28800" windowHeight="15435" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Spoty" sheetId="2" r:id="rId1"/>
@@ -1510,7 +1510,7 @@
         <v>30</v>
       </c>
       <c r="F3" s="3">
-        <v>45127</v>
+        <v>45858</v>
       </c>
       <c r="H3" s="4">
         <v>0.81254629629629627</v>
@@ -1532,7 +1532,7 @@
         <v>30</v>
       </c>
       <c r="F4" s="3">
-        <v>45128</v>
+        <v>45859</v>
       </c>
       <c r="H4" s="4">
         <v>0.8125</v>
@@ -1554,7 +1554,7 @@
         <v>30</v>
       </c>
       <c r="F5" s="3">
-        <v>45129</v>
+        <v>45860</v>
       </c>
       <c r="H5" s="4">
         <v>0.8125</v>
@@ -1576,7 +1576,7 @@
         <v>30</v>
       </c>
       <c r="F6" s="3">
-        <v>45127</v>
+        <v>45858</v>
       </c>
       <c r="H6" s="4">
         <v>0.33320601851851855</v>
@@ -1604,7 +1604,7 @@
         <v>30</v>
       </c>
       <c r="F7" s="3">
-        <v>45128</v>
+        <v>45859</v>
       </c>
       <c r="H7" s="4">
         <v>0.33320601851851855</v>
@@ -1629,7 +1629,7 @@
         <v>30</v>
       </c>
       <c r="F8" s="3">
-        <v>45130</v>
+        <v>45861</v>
       </c>
       <c r="H8" s="4">
         <v>0.85416666666666696</v>
@@ -1651,7 +1651,7 @@
         <v>6</v>
       </c>
       <c r="F9" s="3">
-        <v>45126</v>
+        <v>45857</v>
       </c>
       <c r="J9">
         <v>150000</v>
@@ -1669,7 +1669,7 @@
         <v>7</v>
       </c>
       <c r="F10" s="3">
-        <v>45127</v>
+        <v>45858</v>
       </c>
       <c r="O10" s="5"/>
     </row>
@@ -1684,7 +1684,7 @@
         <v>8</v>
       </c>
       <c r="F11" s="3">
-        <v>45129</v>
+        <v>45860</v>
       </c>
       <c r="O11" s="5"/>
     </row>
@@ -1699,10 +1699,10 @@
         <v>10</v>
       </c>
       <c r="F12" s="3">
-        <v>45119</v>
+        <v>45850</v>
       </c>
       <c r="G12" s="3">
-        <v>45127</v>
+        <v>45858</v>
       </c>
       <c r="K12">
         <v>1000</v>
@@ -1737,10 +1737,10 @@
         <v>71</v>
       </c>
       <c r="F13" s="3">
-        <v>45110</v>
+        <v>45841</v>
       </c>
       <c r="G13" s="3">
-        <v>45110</v>
+        <v>45841</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4"/>
@@ -1771,10 +1771,10 @@
         <v>70</v>
       </c>
       <c r="F14" s="3">
-        <v>45127</v>
+        <v>45858</v>
       </c>
       <c r="G14" s="3">
-        <v>45129</v>
+        <v>45860</v>
       </c>
       <c r="H14" s="4"/>
       <c r="I14" s="4"/>
@@ -1797,10 +1797,10 @@
         <v>44</v>
       </c>
       <c r="F15" s="3">
-        <v>45116</v>
+        <v>45847</v>
       </c>
       <c r="G15" s="3">
-        <v>45119</v>
+        <v>45850</v>
       </c>
       <c r="J15">
         <v>5000</v>
@@ -1824,10 +1824,10 @@
         <v>45</v>
       </c>
       <c r="F16" s="3">
-        <v>45116</v>
+        <v>45847</v>
       </c>
       <c r="G16" s="3">
-        <v>45119</v>
+        <v>45850</v>
       </c>
       <c r="M16" s="5">
         <v>48.603000000000002</v>
@@ -1845,10 +1845,10 @@
         <v>41</v>
       </c>
       <c r="F17" s="3">
-        <v>45116</v>
+        <v>45847</v>
       </c>
       <c r="G17" s="3">
-        <v>45119</v>
+        <v>45850</v>
       </c>
       <c r="M17" s="5">
         <v>48.800080000000001</v>
@@ -1869,10 +1869,10 @@
         <v>240</v>
       </c>
       <c r="F18" s="3">
-        <v>45116</v>
+        <v>45847</v>
       </c>
       <c r="G18" s="3">
-        <v>45119</v>
+        <v>45850</v>
       </c>
       <c r="M18" s="5">
         <v>48.205939999999998</v>
